--- a/stories/arbres/ATOM-EMO.LEX.008-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Louna aide maman dans la cuisine. Papa range les bols. Louna porte un sachet de farine. Le sachet penche. La farine tombe sur la table. Louna sent ses joues chaudes. Son ventre se serre. Elle dit : je suis gênée. C'est une erreur. Une erreur ne dit pas qui elle est. Être gêné, ce n'est pas honteux. Papa s'approche. Louna dit : j'ai versé. Elle prend un torchon. Elle répare. Elle essuie la table. La farine disparaît. Parce qu'elle a dit, elle a pu réparer. Maman dit : merci. Louna souffle. Ses joues se calment. On dit. On répare.</t>
+          <t>Louna aide maman dans la cuisine. Papa range les bols. Louna porte un sachet de farine. Le sachet penche. La farine tombe sur la table. Louna sent ses joues chaudes. Son ventre se serre. Je suis gênée. C'est une erreur. Une erreur ne dit pas qui elle est. Être gêné, ce n'est pas honteux. Papa s'approche. J'ai versé. Elle prend un torchon. Elle répare. Elle essuie la table. La farine disparaît. Parce qu'elle a dit, elle a pu réparer. Merci. Louna souffle. Ses joues se calment. On dit. On répare.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Louna aide maman dans la cuisine. Papa range les bols. Louna porte un sachet de farine. Le sachet penche. La farine tombe sur la table. Louna sent ses joues chaudes. Son ventre se serre.
+narrateur|Je suis gênée. C'est une erreur.
+narrateur|Une erreur ne dit pas qui elle est. Être gêné, ce n'est pas honteux. Papa s'approche.
+enfant-f|J'ai versé.
+narrateur|Elle prend un torchon. Elle répare. Elle essuie la table. La farine disparaît. Parce qu'elle a dit, elle a pu réparer.
+maman|Merci.
+narrateur|Louna souffle. Ses joues se calment. On dit. On répare.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1467,6 +1494,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Louna a versé la farine. Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1491,7 +1523,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Louna a dit : je suis gênée. C'était une erreur. Elle a réparé avec le torchon.</t>
+          <t>Louna Je suis gênée. C'était une erreur. Elle a réparé avec le torchon.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1633,6 +1665,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Louna
+enfant-f|Je suis gênée. C'était une erreur. Elle a réparé avec le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Louna pose le torchon. Papa verse un peu de farine, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Louna souffle. Ses joues se calment. On dit. On répare.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Louna a versé la farine. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,7 @@
 enfant-f|Je suis gênée. C'était une erreur. Elle a réparé avec le torchon.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1846,7 @@
           <t>narrateur|Louna pose le torchon. Papa verse un peu de farine, tout doux.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.008-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Louna est gênée</t>
+          <t>Mila est gênée</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila porte un sachet de farine. La farine tombe. Elle dit qu'elle est gênée. Elle répare avec un torchon.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Louna aide maman dans la cuisine. Papa range les bols. Louna porte un sachet de farine. Le sachet penche. La farine tombe sur la table. Louna sent ses joues chaudes. Son ventre se serre. Je suis gênée. C'est une erreur. Une erreur ne dit pas qui elle est. Être gêné, ce n'est pas honteux. Papa s'approche. J'ai versé. Elle prend un torchon. Elle répare. Elle essuie la table. La farine disparaît. Parce qu'elle a dit, elle a pu réparer. Merci. Louna souffle. Ses joues se calment. On dit. On répare.</t>
+          <t>Un rayon de soleil pose une bande chaude sur le sac de farine. La farine est blanche, comme un nuage arrêté. Une cuillère en bois attend dans un bol. Papa range les bols, un par un. Les bols font un petit bruit de porcelaine. Un sachet de sucre attend près du beurre. Ça sent déjà un peu le gâteau. Mila, tu m'aides pour le gâteau ? Oui, maman. Je porte le sachet. Tout doux, jusqu'à la table. En ce moment, Mila aide dans la cuisine. Elle porte le sachet de farine. Le sachet penche. La farine tombe sur la table. Un petit nuage blanc s'assoit sur le bois. Mila sent ses joues chaudes. Son ventre se serre. Je suis gênée. C'est une erreur. Une erreur ne dit pas qui tu es. Être gêné, ce n'est pas honteux. Papa s'approche. J'ai versé. Merci d'avoir dit. Voici le torchon. Mila prend le torchon. Elle répare. Elle essuie la table. La farine disparaît. Parce que tu as dit, tu as pu réparer. J'ai dit. J'ai réparé. Bravo, Mila. C'est du bon travail. Mila souffle. Ses joues se calment. On dit. On répare. Tes joues sont moins chaudes ? Oui, maman. Le rayon de soleil a bougé un peu. Il touche maintenant la cuillère en bois. On reprend le sachet, ensemble ? Oui. Tout doux, cette fois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,20 +1324,55 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Louna aide maman dans la cuisine. Papa range les bols. Louna porte un sachet de farine. Le sachet penche. La farine tombe sur la table. Louna sent ses joues chaudes. Son ventre se serre.
-narrateur|Je suis gênée. C'est une erreur.
-narrateur|Une erreur ne dit pas qui elle est. Être gêné, ce n'est pas honteux. Papa s'approche.
+          <t>narrateur|Un rayon de soleil pose une bande chaude sur le sac de farine.
+narrateur|La farine est blanche, comme un nuage arrêté.
+narrateur|Une cuillère en bois attend dans un bol.
+narrateur|Papa range les bols, un par un.
+narrateur|Les bols font un petit bruit de porcelaine.
+narrateur|Un sachet de sucre attend près du beurre.
+narrateur|Ça sent déjà un peu le gâteau.
+maman|Mila, tu m'aides pour le gâteau ?
+enfant-f|Oui, maman.
+enfant-f|Je porte le sachet.
+papa|Tout doux, jusqu'à la table.
+narrateur|En ce moment, Mila aide dans la cuisine.
+narrateur|Elle porte le sachet de farine.
+narrateur|Le sachet penche.
+narrateur|La farine tombe sur la table.
+narrateur|Un petit nuage blanc s'assoit sur le bois.
+narrateur|Mila sent ses joues chaudes.
+narrateur|Son ventre se serre.
+enfant-f|Je suis gênée.
+maman|C'est une erreur.
+papa|Une erreur ne dit pas qui tu es.
+papa|Être gêné, ce n'est pas honteux.
+narrateur|Papa s'approche.
 enfant-f|J'ai versé.
-narrateur|Elle prend un torchon. Elle répare. Elle essuie la table. La farine disparaît. Parce qu'elle a dit, elle a pu réparer.
-maman|Merci.
-narrateur|Louna souffle. Ses joues se calment. On dit. On répare.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>enfants_parc</t>
-        </is>
-      </c>
+maman|Merci d'avoir dit.
+maman|Voici le torchon.
+narrateur|Mila prend le torchon.
+narrateur|Elle répare.
+narrateur|Elle essuie la table.
+narrateur|La farine disparaît.
+papa|Parce que tu as dit, tu as pu réparer.
+enfant-f|J'ai dit.
+enfant-f|J'ai réparé.
+maman|Bravo, Mila.
+maman|C'est du bon travail.
+narrateur|Mila souffle.
+narrateur|Ses joues se calment.
+papa|On dit.
+papa|On répare.
+maman|Tes joues sont moins chaudes ?
+enfant-f|Oui, maman.
+narrateur|Le rayon de soleil a bougé un peu.
+narrateur|Il touche maintenant la cuillère en bois.
+papa|On reprend le sachet, ensemble ?
+enfant-f|Oui.
+enfant-f|Tout doux, cette fois.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1350,7 +1397,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Louna a versé la farine. Que fait-elle ?</t>
+          <t>Mila a versé la farine. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1553,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Louna a versé la farine. Que fait-elle ?</t>
+          <t>narrateur|Mila a versé la farine.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1582,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Louna Je suis gênée. C'était une erreur. Elle a réparé avec le torchon.</t>
+          <t>Mila a nommé : gêné. C'était une erreur. Elle a réparé avec le torchon. Je suis gênée. J'ai versé. J'ai réparé. Oui. L'erreur n'est pas toi. Bravo. C'est du bon travail. Un peu de farine reste sur le torchon. On le secoue au-dessus de l'évier ? Oui. Tout doux. On dit. On répare. Le sachet de sucre n'a pas bougé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,8 +1726,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Louna
-enfant-f|Je suis gênée. C'était une erreur. Elle a réparé avec le torchon.</t>
+          <t>narrateur|Mila a nommé : gêné.
+narrateur|C'était une erreur.
+narrateur|Elle a réparé avec le torchon.
+enfant-f|Je suis gênée.
+enfant-f|J'ai versé.
+enfant-f|J'ai réparé.
+papa|Oui.
+papa|L'erreur n'est pas toi.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Un peu de farine reste sur le torchon.
+papa|On le secoue au-dessus de l'évier ?
+enfant-f|Oui.
+enfant-f|Tout doux.
+maman|On dit.
+maman|On répare.
+narrateur|Le sachet de sucre n'a pas bougé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1707,7 +1770,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Louna pose le torchon. Papa verse un peu de farine, tout doux.</t>
+          <t>Mila pose le torchon. Je verse un peu de farine, tout doux. Dans le bol, cette fois. Je tiens le bol. Bravo. Tu aides encore. Tu as dit. Tu as réparé. J'étais gênée. Et l'erreur n'est pas toi. La cuillère en bois attend dans le bol. On mélange, maintenant ? Oui. Pour le gâteau. Le rayon de soleil reste sur le bois. Tu tournes la cuillère ? Oui. Tout autour. Ça sent le gâteau, déjà. Tu as dit. Tu as réparé. Puis on mélange.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1906,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Louna pose le torchon. Papa verse un peu de farine, tout doux.</t>
+          <t>narrateur|Mila pose le torchon.
+papa|Je verse un peu de farine, tout doux.
+papa|Dans le bol, cette fois.
+enfant-f|Je tiens le bol.
+maman|Bravo.
+maman|Tu aides encore.
+maman|Tu as dit.
+maman|Tu as réparé.
+enfant-f|J'étais gênée.
+papa|Et l'erreur n'est pas toi.
+narrateur|La cuillère en bois attend dans le bol.
+maman|On mélange, maintenant ?
+enfant-f|Oui.
+enfant-f|Pour le gâteau.
+narrateur|Le rayon de soleil reste sur le bois.
+papa|Tu tournes la cuillère ?
+enfant-f|Oui.
+enfant-f|Tout autour.
+maman|Ça sent le gâteau, déjà.
+papa|Tu as dit.
+papa|Tu as réparé.
+enfant-f|Puis on mélange.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais gênée. J'ai dit. J'ai réparé. Bravo, Mila. Tu as fait du bon travail. Le rayon de soleil reste sur la table. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2095,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'étais gênée.
+enfant-f|J'ai dit.
+enfant-f|J'ai réparé.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Le rayon de soleil reste sur la table.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon de soleil pose une bande chaude sur le sac de farine. La farine est blanche, comme un nuage arrêté. Une cuillère en bois attend dans un bol. Papa range les bols, un par un. Les bols font un petit bruit de porcelaine. Un sachet de sucre attend près du beurre. Ça sent déjà un peu le gâteau. Mila, tu m'aides pour le gâteau ? Oui, maman. Je porte le sachet. Tout doux, jusqu'à la table. En ce moment, Mila aide dans la cuisine. Elle porte le sachet de farine. Le sachet penche. La farine tombe sur la table. Un petit nuage blanc s'assoit sur le bois. Mila sent ses joues chaudes. Son ventre se serre. Je suis gênée. C'est une erreur. Une erreur ne dit pas qui tu es. Être gêné, ce n'est pas honteux. Papa s'approche. J'ai versé. Merci d'avoir dit. Voici le torchon. Mila prend le torchon. Elle répare. Elle essuie la table. La farine disparaît. Parce que tu as dit, tu as pu réparer. J'ai dit. J'ai réparé. Bravo, Mila. C'est du bon travail. Mila souffle. Ses joues se calment. On dit. On répare. Tes joues sont moins chaudes ? Oui, maman. Le rayon de soleil a bougé un peu. Il touche maintenant la cuillère en bois. On reprend le sachet, ensemble ? Oui. Tout doux, cette fois.</t>
+          <t>Un rayon de soleil pose une bande chaude sur le sac de farine. La farine est blanche, comme un nuage arrêté. Une cuillère en bois attend dans un bol. Papa range les bols, un par un. Les bols font un petit bruit de porcelaine. Un sachet de sucre attend près du beurre. Ça sent déjà un peu le gâteau. Mila, tu m'aides pour le gâteau ? Oui, maman. Je porte le sachet. Tout doux, jusqu'à la table. En ce moment, Mila aide dans la cuisine. Elle porte le sachet de farine. Le sachet penche. La farine tombe sur la table. Un petit nuage blanc s'assoit sur le bois. Mila sent ses joues chaudes. Son ventre se serre. Je suis gênée. C'est une erreur. Une erreur ne dit pas qui tu es. Être gêné, ce n'est pas honteux. Papa s'approche. J'ai versé. Merci d'avoir dit. Voici le torchon. Mila prend le torchon. Elle répare. Elle essuie la table. La farine disparaît. Parce que tu as dit, tu as pu réparer. J'ai dit. J'ai réparé. Bravo, Mila. Mila souffle. Ses joues se calment. On dit. On répare. Tes joues sont moins chaudes ? Oui, maman. Le rayon de soleil a bougé un peu. Il touche maintenant la cuillère en bois. On reprend le sachet, ensemble ? Oui. Tout doux, cette fois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Louna aide maman dans la cuisine. Papa range les bols. Louna porte un sachet de farine. Le sachet penche. La farine tombe sur la table. Louna sent ses joues chaudes. Son ventre se serre. Elle dit : je suis &lt;emphasis level="moderate"&gt;gêné&lt;/emphasis&gt;e. C'est une erreur. Une erreur ne dit pas qui elle est. Être gêné, ce n'est pas honteux. Papa s'approche. Louna dit : j'ai versé. Elle prend un torchon. Elle répare. Elle essuie la table. La farine disparaît. Parce qu'elle a dit, elle a pu réparer. Maman dit : merci. Louna souffle. Ses joues se calment. On dit. On répare.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon de soleil pose une bande chaude sur le sac de farine. La farine est blanche, comme un nuage arrêté. Une cuillère en bois attend dans un bol. Papa range les bols, un par un. Les bols font un petit bruit de porcelaine. Un sachet de sucre attend près du beurre. Ça sent déjà un peu le gâteau. Mila, tu m'aides pour le gâteau ? Oui, maman. Je porte le sachet. Tout doux, jusqu'à la table. En ce moment, Mila aide dans la cuisine. Elle porte le sachet de farine. Le sachet penche. La farine tombe sur la table. Un petit nuage blanc s'assoit sur le bois. Mila sent ses joues chaudes. Son ventre se serre. Je suis gênée. C'est une erreur. Une erreur ne dit pas qui tu es. Être gêné, ce n'est pas honteux. Papa s'approche. J'ai versé. Merci d'avoir dit. Voici le torchon. Mila prend le torchon. Elle répare. Elle essuie la table. La farine disparaît. Parce que tu as dit, tu as pu réparer. J'ai dit. J'ai réparé. Bravo, Mila. Mila souffle. Ses joues se calment. On dit. On répare. Tes joues sont moins chaudes ? Oui, maman. Le rayon de soleil a bougé un peu. Il touche maintenant la cuillère en bois. On reprend le sachet, ensemble ? Oui. Tout doux, cette fois.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1358,7 +1358,6 @@
 enfant-f|J'ai dit.
 enfant-f|J'ai réparé.
 maman|Bravo, Mila.
-maman|C'est du bon travail.
 narrateur|Mila souffle.
 narrateur|Ses joues se calment.
 papa|On dit.
@@ -1372,7 +1371,6 @@
 enfant-f|Tout doux, cette fois.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1402,7 +1400,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Louna a versé la farine. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a versé la farine. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1557,7 +1555,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1582,12 +1579,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a nommé : gêné. C'était une erreur. Elle a réparé avec le torchon. Je suis gênée. J'ai versé. J'ai réparé. Oui. L'erreur n'est pas toi. Bravo. C'est du bon travail. Un peu de farine reste sur le torchon. On le secoue au-dessus de l'évier ? Oui. Tout doux. On dit. On répare. Le sachet de sucre n'a pas bougé.</t>
+          <t>Mila a nommé : gêné. C'était une erreur. Elle a réparé avec le torchon. Je suis gênée. J'ai versé. J'ai réparé. Oui. L'erreur n'est pas toi. Bravo. Un peu de farine reste sur le torchon. On le secoue au-dessus de l'évier ? Oui. Tout doux. On dit. On répare. Le sachet de sucre n'a pas bougé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Louna a dit : je suis &lt;emphasis level="moderate"&gt;gêné&lt;/emphasis&gt;e. C'était une erreur. Elle a réparé avec le torchon.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a nommé : gêné. C'était une erreur. Elle a réparé avec le torchon. Je suis gênée. J'ai versé. J'ai réparé. Oui. L'erreur n'est pas toi. Bravo. Un peu de farine reste sur le torchon. On le secoue au-dessus de l'évier ? Oui. Tout doux. On dit. On répare. Le sachet de sucre n'a pas bougé.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1735,7 +1732,6 @@
 papa|Oui.
 papa|L'erreur n'est pas toi.
 maman|Bravo.
-maman|C'est du bon travail.
 narrateur|Un peu de farine reste sur le torchon.
 papa|On le secoue au-dessus de l'évier ?
 enfant-f|Oui.
@@ -1745,7 +1741,6 @@
 narrateur|Le sachet de sucre n'a pas bougé.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1775,7 +1770,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Louna pose le torchon. Papa verse un peu de farine, tout doux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila pose le torchon. Je verse un peu de farine, tout doux. Dans le bol, cette fois. Je tiens le bol. Bravo. Tu aides encore. Tu as dit. Tu as réparé. J'étais gênée. Et l'erreur n'est pas toi. La cuillère en bois attend dans le bol. On mélange, maintenant ? Oui. Pour le gâteau. Le rayon de soleil reste sur le bois. Tu tournes la cuillère ? Oui. Tout autour. Ça sent le gâteau, déjà. Tu as dit. Tu as réparé. Puis on mélange.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1930,7 +1925,6 @@
 enfant-f|Puis on mélange.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1955,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais gênée. J'ai dit. J'ai réparé. Bravo, Mila. Tu as fait du bon travail. Le rayon de soleil reste sur la table. L'histoire est finie.</t>
+          <t>J'étais gênée. J'ai dit. J'ai réparé. Bravo, Mila. Le rayon de soleil reste sur la table.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais gênée. J'ai dit. J'ai réparé. Bravo, Mila. Le rayon de soleil reste sur la table.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,12 +2093,9 @@
 enfant-f|J'ai dit.
 enfant-f|J'ai réparé.
 maman|Bravo, Mila.
-papa|Tu as fait du bon travail.
-narrateur|Le rayon de soleil reste sur la table.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le rayon de soleil reste sur la table.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2159,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Louna, papa, maman</t>
+          <t>Mila, papa, maman</t>
         </is>
       </c>
     </row>
